--- a/datasets/merged_datasets/General_data_merged.xlsx
+++ b/datasets/merged_datasets/General_data_merged.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miles\Downloads\progetto_bda-main\Merge_datasets_output\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\miles\Downloads\progetto_bda-main\datasets\Merge_datasets_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B509F1C1-365A-435B-BD88-7EF5961DE237}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131EDCF6-52B4-4EEE-8DF2-3C72832D3957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="323">
-  <si>
-    <t>name_x</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="321">
+  <si>
+    <t>name</t>
   </si>
   <si>
     <t>address_x</t>
@@ -40,10 +40,7 @@
     <t>url_x</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name_y</t>
+    <t>id_x</t>
   </si>
   <si>
     <t>address_y</t>
@@ -59,6 +56,9 @@
   </si>
   <si>
     <t>url_y</t>
+  </si>
+  <si>
+    <t>id_y</t>
   </si>
   <si>
     <t>fattoria country village</t>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t>https://www.booking.com/hotel/it/la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona.it.html</t>
+  </si>
+  <si>
+    <t>la-bolla-del-borgo-le-marche-tra-le-stelle-provincia-di-ancona</t>
   </si>
   <si>
     <t>CAMPING TRE ARCHI</t>
@@ -423,24 +426,6 @@
     <t>casale-civetta</t>
   </si>
   <si>
-    <t>Casale Civetta</t>
-  </si>
-  <si>
-    <t>Via Consolazione 20, 60012 Borgo della Consolazione, Trecastelli Italia</t>
-  </si>
-  <si>
-    <t>Casale Civetta ha un parco alberato con sentieri per passeggiate interne interrotte da tavoli in pietra. Ampi spazi aperti, pavimentati con mattoni dove camminare a piedi nudi.Una piscina panoramica sulle colline.Un laboratorio di scultura del tufo.Alberi da frutto. Animali in libertà, pesci, gatti e galline. Amicizia, familiarità,semplicità,arte,accoglienza e condivisione della propria umanità.</t>
-  </si>
-  <si>
-    <t>non disponibile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Lezioni di yoga, Bar a bordo piscina, Spiaggia, Noleggio di biciclette, Attività per bambini/famiglie, Parcheggio custodito, Wi-Fi, Teli da piscina/mare, Piscina con vista, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Pasti per bambini, Giochi all'aperto per bambini, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio navetta, Sale riunioni, Area barbecue, Deposito bagagli, Hotel per non fumatori, Arredi esterni, Area picnic, Lettini/sedie sdraio, Terrazza solarium, Reception 24 ore su 24, Servizio lavanderia, Acqua in bottiglia, Angolo cottura, Camere per famiglie, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.it/Hotel_Review-g23906399-d12336250-Reviews-Casale_Civetta-Borgo_della_Consolazione_Trecastelli_Province_of_Ancona_Marche.html</t>
-  </si>
-  <si>
     <t>Tobacco Road camping Sirolo</t>
   </si>
   <si>
@@ -528,6 +513,9 @@
     <t xml:space="preserve"> 	La vacanza al Camping Blu è all'insegna del comfort e del relax.Al Camping Blu sono disponibili piazzole ombreggiate e spaziose per tende, camper e caravan a pochi metri dal mare.A disposizione degli ospiti anche moderne case mobili climatizzate, confortevoli appartamenti, piscine, parco giochi e campo da beach volley.</t>
   </si>
   <si>
+    <t>non disponibile</t>
+  </si>
+  <si>
     <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Ristorante, Spiaggia, Noleggio di biciclette, Parco giochi per bambini, Area giochi interna per bambini, Parcheggio custodito, Wi-Fi, Vasca idromassaggio, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Zona pranzo all'aperto, Snack bar, Aerobica, Freccette, Personale di intrattenimento, Intrattenimento serale, Ping pong, Attività per bambini/famiglie, Miniclub, Giochi all'aperto per bambini, Area barbecue, Minimarket, Hotel per non fumatori, Lounge/sala TV in comune, Lettini/sedie sdraio, Ombrelloni, Asciugatrice, Aria condizionata, Zona soggiorno, Divano, Appendiabiti, Bollitore per tè/caffè, Angolo cottura, TV a schermo piatto, Bidet, Bagni privati, Frigorifero, Piano cottura, Utensili da cucina, Cabina doccia, Camere non fumatori, Camere per famiglie, </t>
   </si>
   <si>
@@ -579,6 +567,21 @@
   </si>
   <si>
     <t>villaggio-cortina</t>
+  </si>
+  <si>
+    <t>Lungomare Italia 1/1, 60019, Senigallia Italia</t>
+  </si>
+  <si>
+    <t>Il camping è perfetto per chi viaggia con il proprio cane. Le mobile homes sono molto datate e necessitato di manutenzione ma per chi si adatta vanno bene. Ottimo che siano recintate per permettere ai cani di stare liberi. La spiaggia per cani è a due passi. Il posto è molto tranquillo ma totalmente privo di servizi. Il primo supermercato è a 2km quindi è essenziale che il camping pensi di aprire un minimarket almeno per i prodotti freschi e di base. Il bar è molto scarno. La ferrovia passa a circa 20 metri dalle casette ma personalmente non ci facevo troppo caso. Il campeggio in generale seppur vecchio è pulito. Tornerei perché è una vacanza a misura di cane e all'insegna del relax ma devono necessariamente garantire qualche servizio in più, anche perché spostandosi di pochi chilometri si possono trovare altre bau beach con annessi campeggi molto più vicine ai servizi.…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Bar/lounge, Spiaggia, Noleggio di biciclette, Miniclub, Giochi all'aperto per bambini, Animali domestici ammessi, Parcheggio in strada, Ristorante, Pasti per bambini, Snack bar, Personale di intrattenimento, Intrattenimento serale, Ping pong, Servizio navetta, Area barbecue, Minimarket, Hotel per non fumatori, Servizio lavanderia, Aria condizionata, Spiaggia privata, Zona soggiorno, Acqua in bottiglia, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.it/Hotel_Review-g194914-d3309922-Reviews-Camping_Villaggio_Cortina-Senigallia_Province_of_Ancona_Marche.html</t>
+  </si>
+  <si>
+    <t>camping-villaggio-cortina</t>
   </si>
   <si>
     <t>Camping Spiaggia di Velluto</t>
@@ -796,7 +799,133 @@
     <t>poggio-imperiale-marche</t>
   </si>
   <si>
-    <t>Poggio Imperiale Marche</t>
+    <t>Natural Village Resort</t>
+  </si>
+  <si>
+    <t>Strada Statale 16, Km. 331,48 Contrada Torrenova, 62018 Porto Potenza Picena, Potenza Picena Italia</t>
+  </si>
+  <si>
+    <t>Il Natural Village Resort è un prestigioso villaggio turistico della Riviera Adriatica a due passi della Riviera del Conero, a Potenza Picena nelle Marche. Si estende per 6 ettari ed è composto da 245 chalet in legno immersi nel verde. Si affaccia direttamente sul mare Bandiera Blu, con spiaggia privata ed attrezzata con lettini ed ombrelloni. A poca distanza da Porto Recanati e dalle principali località di Portonovo, Sirolo, Numana, Marcelli e la bellissima città di Ancona, il Natural Village Resort è un vero paradiso per chi ama il mare, il relax, lo sport e la natura. Non perdere l’opportunità di vivere una vacanza indimenticabile in famiglia, in coppia e con gli amici. I vostri amici a 4 zampe sono i benvenuti al Natural Village Resort. I bellissimi chalet del Natural Village Resort sono molto confortevoli, sono in legno dipinto con pitture assolutamente ecologiche e l’intero villaggio è costruito a bassa cementificazione nel totale rispetto dell’ambiente. Gli chalet si armonizzano con il paesaggio circostante, arricchendolo. In più: tre bar, due ristoranti, il mini-market, la pizzeria &amp; Take Away, il campetto polivalente per calcio e tennis, noleggio biciclette e numerose aree giochi attrezzate per bambini. L’animazione presente organizza ogni giorno tante attività divertenti e coinvolgenti per gli ospiti, grandi e piccoli: giochi, tornei, spettacoli… Internet wireless per tutto il villaggio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcheggio gratuito, Piscina, Lezioni di yoga, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Parcheggio custodito, Teli da piscina/mare, Piscina all'aperto, Corsi di fitness, Ristorante, Colazione a buffet, Drink di benvenuto omaggio, Noleggio di biciclette, Canoismo, Campo da tennis, Noleggi di attrezzature per sport acquatici, Windsurf, Tour in bicicletta, Personale di intrattenimento, Intrattenimento serale, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Servizio taxi, Sicurezza 24 ore su 24, Minimarket, Zanzariera, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Lavanderia self-service, Lavatrice, Camere insonorizzate, Aria condizionata, Spiaggia privata, Servizio di pulizia, Angolo cottura, TV a schermo piatto, Divano letto, Bidet, Cassaforte, Zona soggiorno, Divano, Armadio/cabina, Forno, Frigorifero, Piano cottura, Utensili da cucina, Cabina doccia, Asciugacapelli, Camere non fumatori, Camere per famiglie, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.it/Hotel_Review-g1924689-d948494-Reviews-Natural_Village_Resort-Porto_Potenza_Picena_Potenza_Picena_Province_of_Macerata_Marche.html</t>
+  </si>
+  <si>
+    <t>natural-village-resort</t>
+  </si>
+  <si>
+    <t>La Risacca Camping Village - Formule Hotel</t>
+  </si>
+  <si>
+    <t>Via Europa 100, 63821 Porto Sant'Elpidio Italia</t>
+  </si>
+  <si>
+    <t>Il nostro ristorante è all'interno di La Risacca Family Camping Village, situato a lato della Piazza, dove si svolgono tutte le attività di animazione e intrattenimento serale. Lambiente marinaro del ristorante è intimo, cordiale e accogliente, vi si respira una fresca atmosfera familiare. Dispone di una ampia sala interna climatizzata e di tavoli all'esterno sotto un porticato e in una terrazza attrezzata. Il nostro ristorante è affiliato AIC (Associazione Italiana Celiachia) ed è possibile mangiare senza glutine in tutta sicurezza. Il menù è stato studiato per accontentare i gusti di una tipica famiglia italiana: carne, pesce, pizza, specialità della zona.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Wi-Fi, Giochi da piscina, Piscina all'aperto, Piscina con estremità bassa, Ristorante, Colazione disponibile, Pasti per bambini, Menù dietetici speciali, Bar in piscina, Noleggio di biciclette, Canoismo, Escursioni, Campo da tennis, Parco acquatico, Windsurf, Aerobica, Personale di intrattenimento, Intrattenimento serale, Ping pong, Scivolo acquatico, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Passeggini, Animali domestici ammessi, Area barbecue, Minimarket, Negozio di articoli da regalo, Quotidiano, Negozi, Lettini/sedie sdraio, Ombrelloni, Bancomat in loco, Infermeria, Lavanderia self-service, Aria condizionata, Spiaggia privata, Servizio di pulizia, Cassaforte, Angolo cottura, Frigorifero, TV a schermo piatto, Bagno/doccia, Zona soggiorno, Piano cottura, Utensili da cucina, Camere non fumatori, Camere per famiglie, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.it/Hotel_Review-g1582949-d2346767-Reviews-La_Risacca_Camping_Village_Formule_Hotel-Porto_Sant_Elpidio_Province_of_Fermo_Marche.html</t>
+  </si>
+  <si>
+    <t>la-risacca-camping-village</t>
+  </si>
+  <si>
+    <t>Girasole Eco Family Village</t>
+  </si>
+  <si>
+    <t>Via Marina Palmense, 63900 Marina Palmense, Fermo Italia</t>
+  </si>
+  <si>
+    <t>Complesso ricettivo direttamente sul mare, immerso in una vegetazione rigogliosa, in cui troverete spaziosi chalet in legno e confortevoli case mobili, acquapark con piscina e scivolo e vasche idromassaggio, spiaggia attrezzata, ristorante-bar, supermercato, parco giochi e tanti servizi per una vacanza di divertimento e relax.</t>
+  </si>
+  <si>
+    <t>24 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Campo da tennis, Attività per bambini/famiglie, Miniclub, Wi-Fi, Vasca idromassaggio, Piscina all'aperto, Ristorante, Bar in piscina, Bar a bordo piscina, Personale di intrattenimento, Intrattenimento serale, Ping pong, Giochi all'aperto per bambini, Animali domestici ammessi, Minimarket, Servizio lavanderia, Lavanderia self-service, Aria condizionata, Spiaggia privata, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Vista sull'oceano, Camere non fumatori, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.it/Hotel_Review-g1741825-d1891906-Reviews-Girasole_Eco_Family_Village-Marina_Palmense_Fermo_Province_of_Fermo_Marche.html</t>
+  </si>
+  <si>
+    <t>girasole-eco-family-village</t>
+  </si>
+  <si>
+    <t>Green Garden Camping Village</t>
+  </si>
+  <si>
+    <t>Via Peschiera, 3, 60020 Sirolo Italia</t>
+  </si>
+  <si>
+    <t>Ho soggiornato in questo villaggio con la mia famiglia per una settimana. Villaggio situato in una zona tranquilla, immerso nel verde e ben ventilata (non si affaccia sul mare ma c’è una navetta che vi porterà e vi riporterà al villaggio).  Abbiamo preso una casetta (mobil standard home per 5 persone) carina ed essenziale con un patio esterno dove poter mangiare.  All’interno del villaggio c’è una piscina, campo da beach volley, da calcio, da tennis e un bar/ristorante/pizzeria. Tutto sommato ci siamo trovati bene, l’unica nota negativa è che non è presente un supermercato all’interno del villaggio.  Come ultima cosa il villaggio ha un bagno convenzionato ( stabilimento Eugenio) con un ombrellone e due lettini compresi nel prezzo.  Personale gentile ed efficiente.  Lo consiglio a chi vuole rilassarsi nelle zone del Sirolo.…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcheggio gratuito, Wi-Fi, Piscina, Bar/lounge, Escursioni, Campo da tennis, Parco giochi per bambini, Attività per bambini/famiglie, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Snack bar, Ping pong, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Area barbecue, Deposito bagagli, Zanzariera, Lounge/sala TV in comune, Lettini/sedie sdraio, Terrazza solarium, Ombrelloni, Cassetta di pronto soccorso, Asciugatrice, Lavanderia self-service, Spiaggia privata, Angolo cottura, Frigorifero, TV a schermo piatto, Camere per famiglie, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.it/Hotel_Review-g608900-d1146098-Reviews-Green_Garden_Camping_Village-Sirolo_Province_of_Ancona_Marche.html</t>
+  </si>
+  <si>
+    <t>green-garden-camping-village</t>
+  </si>
+  <si>
+    <t>Centro Vacanze Garden River</t>
+  </si>
+  <si>
+    <t>Via Ottorino Respighi snc, 63824 Altidona Italia</t>
+  </si>
+  <si>
+    <t>Abitato per due settimane in una MOBILEHOME nuova e molto funzionale (appena consegnate), con ottima insonorizzazione e climatizzazioni, avente un patio di legno esterno bello e comodo, peccato che le doghe erano troppo larghe e il cane ci passava attraverso (mettere una rete no?). Punti di forza sono la tranquillità e l'accoglienza del personale, giovane e sempre disponibile e gli spazi obiettivamente ampi. Il mare non è vicino, ci sono 2 spiagge a disposizione (ciottoli e sabbia) raggiungibili con una strada ciclabile (ma solo per metà) che prevede una bella passeggiata altrimenti c'è Gabriele con la sua Navetta ad orari prestabiliti. Ristorante buono e abbastanza vario nelle pietanze. Disponibile campo da calcio (o meglio due porte) una rete da pallavolo con campo in sabbia, calciobalilla (a pagamento) e tavolo da tennistavolo. Piscina abbastanza grande e pulita. Citazioni particolari per la Sig.a MARZIA delle pulizie, professionale e sempre disponibile, un saluto ad Alessia del Bar e al già nominato Gabriele. Punti carenti: - la prima settimana animazione praticamente inesistente...si sono ripresi un pò nella seconda settimana; - l'area cani e il camping sprovvisti dei minimi requisiti per definirsi PET FRIENDLY, nessun omaggio di benvenuto (come indicato dal sito), niente cestini dove buttare gli escrementi dei cani e niente bustine per prenderli....niente doccette specifiche e quelle per "umani" molto difficile da trovare per mancanza di indicazioni, area cani priva di secchi, fonti di acqua e ombra! - un pò troppe mosche e formiche; Consiglio vivamente di portare scarpette da scoglio per andare al mare specialmente per la spiaggia di ciottoli, una racchetta per uccidere le zanzare e mosche, canavacci per la cucina (non forniti).…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Piscina, Bar/lounge, Noleggio di biciclette, Biciclette disponibili, Area giochi interna per bambini, Attività per bambini/famiglie, Internet, Piscina a sfioro, Piscina per adulti, Piscina all'aperto, Piscina piccola, Piscina recintata, Ristorante, Colazione disponibile, Freccette, Intrattenimento serale, Pesca, Karaoke, Ping pong, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Navetta o servizio taxi gratis, Servizio navetta, Hotel per non fumatori, Angolo cottura, Frigorifero, Utensili da cucina, Camere non fumatori, Camere per famiglie, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.it/Hotel_Review-g2189383-d4923901-Reviews-Centro_Vacanze_Garden_River-Altidona_Province_of_Fermo_Marche.html</t>
+  </si>
+  <si>
+    <t>centro-vacanze-garden-river</t>
+  </si>
+  <si>
+    <t>Amapolas Villaggio &amp; Camping</t>
+  </si>
+  <si>
+    <t>225 Via Villagrande, 61024 Mombaroccio Italia</t>
+  </si>
+  <si>
+    <t>Amapolas Villaggio è situato tra le dolci colline di Villagrande di Mombaroccio, punto di partenza ideale per vivere i sapori e i colori delle Marche. A disposizione dei nostri ospiti casette mobili di diverse dimensioni in cui soggiornare nel comfort più totale: dotate di cucina attrezzata, bagno con doccia, aria condizionata e patio con vista sul paesaggio rurale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcheggio gratuito, Animali domestici ammessi, Angolo cottura, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.it/Hotel_Review-g2136886-d21340843-Reviews-Amapolas_Villaggio_Camping-Mombaroccio_Province_of_Pesaro_and_Urbino_Marche.html</t>
+  </si>
+  <si>
+    <t>amapolas-villaggio-&amp;-camping</t>
+  </si>
+  <si>
+    <t>Residence Mare</t>
+  </si>
+  <si>
+    <t>Via Ugo La Malfa 19 Località Lido San Tommaso, 63900, Fermo Italia</t>
+  </si>
+  <si>
+    <t>Il Villaggio Turistico Residence Mare si trova nel centro abitato di Lido San Tommaso sul lungomare nord di Fermo ed è un luogo ideale per famiglie con bambini e coppie poichè è tranquillo, essendo di piccole dimensioni e senza il frastuono stradale o ferroviario. Si trova sulla spiaggia libera alla quale si accede direttamente (senza alcun costo d'ingresso), composta di sabbia e ghiaia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Caffetteria, Noleggio di biciclette, Aerobica, Servizio di babysitter, Parco giochi per bambini, Wi-Fi, Ristorante, Colazione disponibile, Pasti per bambini, Zona pranzo all'aperto, Freccette, Personale di intrattenimento, Intrattenimento serale, Pesca, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio taxi, Trattamenti per il viso, Massaggio completo, Manicure, Massaggio, Servizi di ceretta, Accesso diretto alle piste da sci, Sicurezza 24 ore su 24, Area barbecue, Concierge, Hotel per non fumatori, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Ombrello, Check-in/check-out express, Servizio lavanderia, Lavanderia self-service, Servizio stireria, Purificatore d'aria, Aria condizionata, Servizio di pulizia, Balcone privato, Bagni privati, Angolo cottura, TV satellitare/via cavo, Bidet, Pavimento in piastrelle/marmo, Frigorifero, Piano cottura, Utensili da cucina, TV a schermo piatto, Cabina doccia, Asciugacapelli, Vista sulla piscina, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.it/Hotel_Review-g1025201-d677045-Reviews-Villaggio_Turistico_Residence_Mare-Fermo_Province_of_Fermo_Marche.html</t>
+  </si>
+  <si>
+    <t>residence-mare</t>
   </si>
   <si>
     <t>18 Contrada San Savino, 62012, Civitanova Marche Italia</t>
@@ -808,385 +937,250 @@
     <t>https://www.tripadvisor.it/Hotel_Review-g194742-d21379810-Reviews-Poggio_Imperiale_Marche-Civitanova_Marche_Province_of_Macerata_Marche.html</t>
   </si>
   <si>
-    <t>natural-village-resort</t>
-  </si>
-  <si>
-    <t>Natural Village Resort</t>
-  </si>
-  <si>
-    <t>Strada Statale 16, Km. 331,48 Contrada Torrenova, 62018 Porto Potenza Picena, Potenza Picena Italia</t>
-  </si>
-  <si>
-    <t>Il Natural Village Resort è un prestigioso villaggio turistico della Riviera Adriatica a due passi della Riviera del Conero, a Potenza Picena nelle Marche. Si estende per 6 ettari ed è composto da 245 chalet in legno immersi nel verde. Si affaccia direttamente sul mare Bandiera Blu, con spiaggia privata ed attrezzata con lettini ed ombrelloni. A poca distanza da Porto Recanati e dalle principali località di Portonovo, Sirolo, Numana, Marcelli e la bellissima città di Ancona, il Natural Village Resort è un vero paradiso per chi ama il mare, il relax, lo sport e la natura. Non perdere l’opportunità di vivere una vacanza indimenticabile in famiglia, in coppia e con gli amici. I vostri amici a 4 zampe sono i benvenuti al Natural Village Resort. I bellissimi chalet del Natural Village Resort sono molto confortevoli, sono in legno dipinto con pitture assolutamente ecologiche e l’intero villaggio è costruito a bassa cementificazione nel totale rispetto dell’ambiente. Gli chalet si armonizzano con il paesaggio circostante, arricchendolo. In più: tre bar, due ristoranti, il mini-market, la pizzeria &amp; Take Away, il campetto polivalente per calcio e tennis, noleggio biciclette e numerose aree giochi attrezzate per bambini. L’animazione presente organizza ogni giorno tante attività divertenti e coinvolgenti per gli ospiti, grandi e piccoli: giochi, tornei, spettacoli… Internet wireless per tutto il villaggio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcheggio gratuito, Piscina, Lezioni di yoga, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Parcheggio custodito, Teli da piscina/mare, Piscina all'aperto, Corsi di fitness, Ristorante, Colazione a buffet, Drink di benvenuto omaggio, Noleggio di biciclette, Canoismo, Campo da tennis, Noleggi di attrezzature per sport acquatici, Windsurf, Tour in bicicletta, Personale di intrattenimento, Intrattenimento serale, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Servizio taxi, Sicurezza 24 ore su 24, Minimarket, Zanzariera, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Lavanderia self-service, Lavatrice, Camere insonorizzate, Aria condizionata, Spiaggia privata, Servizio di pulizia, Angolo cottura, TV a schermo piatto, Divano letto, Bidet, Cassaforte, Zona soggiorno, Divano, Armadio/cabina, Forno, Frigorifero, Piano cottura, Utensili da cucina, Cabina doccia, Asciugacapelli, Camere non fumatori, Camere per famiglie, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.it/Hotel_Review-g1924689-d948494-Reviews-Natural_Village_Resort-Porto_Potenza_Picena_Potenza_Picena_Province_of_Macerata_Marche.html</t>
-  </si>
-  <si>
-    <t>la-risacca-camping-village</t>
-  </si>
-  <si>
-    <t>La Risacca Camping Village - Formule Hotel</t>
-  </si>
-  <si>
-    <t>Via Europa 100, 63821 Porto Sant'Elpidio Italia</t>
-  </si>
-  <si>
-    <t>Il nostro ristorante è all'interno di La Risacca Family Camping Village, situato a lato della Piazza, dove si svolgono tutte le attività di animazione e intrattenimento serale. Lambiente marinaro del ristorante è intimo, cordiale e accogliente, vi si respira una fresca atmosfera familiare. Dispone di una ampia sala interna climatizzata e di tavoli all'esterno sotto un porticato e in una terrazza attrezzata. Il nostro ristorante è affiliato AIC (Associazione Italiana Celiachia) ed è possibile mangiare senza glutine in tutta sicurezza. Il menù è stato studiato per accontentare i gusti di una tipica famiglia italiana: carne, pesce, pizza, specialità della zona.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Tiro con l'arco, Parco giochi per bambini, Area giochi interna per bambini, Wi-Fi, Giochi da piscina, Piscina all'aperto, Piscina con estremità bassa, Ristorante, Colazione disponibile, Pasti per bambini, Menù dietetici speciali, Bar in piscina, Noleggio di biciclette, Canoismo, Escursioni, Campo da tennis, Parco acquatico, Windsurf, Aerobica, Personale di intrattenimento, Intrattenimento serale, Ping pong, Scivolo acquatico, Attività per bambini/famiglie, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Passeggini, Animali domestici ammessi, Area barbecue, Minimarket, Negozio di articoli da regalo, Quotidiano, Negozi, Lettini/sedie sdraio, Ombrelloni, Bancomat in loco, Infermeria, Lavanderia self-service, Aria condizionata, Spiaggia privata, Servizio di pulizia, Cassaforte, Angolo cottura, Frigorifero, TV a schermo piatto, Bagno/doccia, Zona soggiorno, Piano cottura, Utensili da cucina, Camere non fumatori, Camere per famiglie, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.it/Hotel_Review-g1582949-d2346767-Reviews-La_Risacca_Camping_Village_Formule_Hotel-Porto_Sant_Elpidio_Province_of_Fermo_Marche.html</t>
-  </si>
-  <si>
-    <t>girasole-eco-family-village</t>
-  </si>
-  <si>
-    <t>Girasole Eco Family Village</t>
-  </si>
-  <si>
-    <t>Via Marina Palmense, 63900 Marina Palmense, Fermo Italia</t>
-  </si>
-  <si>
-    <t>Complesso ricettivo direttamente sul mare, immerso in una vegetazione rigogliosa, in cui troverete spaziosi chalet in legno e confortevoli case mobili, acquapark con piscina e scivolo e vasche idromassaggio, spiaggia attrezzata, ristorante-bar, supermercato, parco giochi e tanti servizi per una vacanza di divertimento e relax.</t>
-  </si>
-  <si>
-    <t>24 €</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Bar/lounge, Spiaggia, Campo da tennis, Attività per bambini/famiglie, Miniclub, Wi-Fi, Vasca idromassaggio, Piscina all'aperto, Ristorante, Bar in piscina, Bar a bordo piscina, Personale di intrattenimento, Intrattenimento serale, Ping pong, Giochi all'aperto per bambini, Animali domestici ammessi, Minimarket, Servizio lavanderia, Lavanderia self-service, Aria condizionata, Spiaggia privata, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Vista sull'oceano, Camere non fumatori, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.it/Hotel_Review-g1741825-d1891906-Reviews-Girasole_Eco_Family_Village-Marina_Palmense_Fermo_Province_of_Fermo_Marche.html</t>
-  </si>
-  <si>
-    <t>green-garden-camping-village</t>
-  </si>
-  <si>
-    <t>Green Garden Camping Village</t>
-  </si>
-  <si>
-    <t>Via Peschiera, 3, 60020 Sirolo Italia</t>
-  </si>
-  <si>
-    <t>Ho soggiornato in questo villaggio con la mia famiglia per una settimana. Villaggio situato in una zona tranquilla, immerso nel verde e ben ventilata (non si affaccia sul mare ma c’è una navetta che vi porterà e vi riporterà al villaggio).  Abbiamo preso una casetta (mobil standard home per 5 persone) carina ed essenziale con un patio esterno dove poter mangiare.  All’interno del villaggio c’è una piscina, campo da beach volley, da calcio, da tennis e un bar/ristorante/pizzeria. Tutto sommato ci siamo trovati bene, l’unica nota negativa è che non è presente un supermercato all’interno del villaggio.  Come ultima cosa il villaggio ha un bagno convenzionato ( stabilimento Eugenio) con un ombrellone e due lettini compresi nel prezzo.  Personale gentile ed efficiente.  Lo consiglio a chi vuole rilassarsi nelle zone del Sirolo.…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcheggio gratuito, Wi-Fi, Piscina, Bar/lounge, Escursioni, Campo da tennis, Parco giochi per bambini, Attività per bambini/famiglie, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Snack bar, Ping pong, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Area barbecue, Deposito bagagli, Zanzariera, Lounge/sala TV in comune, Lettini/sedie sdraio, Terrazza solarium, Ombrelloni, Cassetta di pronto soccorso, Asciugatrice, Lavanderia self-service, Spiaggia privata, Angolo cottura, Frigorifero, TV a schermo piatto, Camere per famiglie, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.it/Hotel_Review-g608900-d1146098-Reviews-Green_Garden_Camping_Village-Sirolo_Province_of_Ancona_Marche.html</t>
-  </si>
-  <si>
-    <t>centro-vacanze-garden-river</t>
-  </si>
-  <si>
-    <t>Centro Vacanze Garden River</t>
-  </si>
-  <si>
-    <t>Via Ottorino Respighi snc, 63824 Altidona Italia</t>
-  </si>
-  <si>
-    <t>Abitato per due settimane in una MOBILEHOME nuova e molto funzionale (appena consegnate), con ottima insonorizzazione e climatizzazioni, avente un patio di legno esterno bello e comodo, peccato che le doghe erano troppo larghe e il cane ci passava attraverso (mettere una rete no?). Punti di forza sono la tranquillità e l'accoglienza del personale, giovane e sempre disponibile e gli spazi obiettivamente ampi. Il mare non è vicino, ci sono 2 spiagge a disposizione (ciottoli e sabbia) raggiungibili con una strada ciclabile (ma solo per metà) che prevede una bella passeggiata altrimenti c'è Gabriele con la sua Navetta ad orari prestabiliti. Ristorante buono e abbastanza vario nelle pietanze. Disponibile campo da calcio (o meglio due porte) una rete da pallavolo con campo in sabbia, calciobalilla (a pagamento) e tavolo da tennistavolo. Piscina abbastanza grande e pulita. Citazioni particolari per la Sig.a MARZIA delle pulizie, professionale e sempre disponibile, un saluto ad Alessia del Bar e al già nominato Gabriele. Punti carenti: - la prima settimana animazione praticamente inesistente...si sono ripresi un pò nella seconda settimana; - l'area cani e il camping sprovvisti dei minimi requisiti per definirsi PET FRIENDLY, nessun omaggio di benvenuto (come indicato dal sito), niente cestini dove buttare gli escrementi dei cani e niente bustine per prenderli....niente doccette specifiche e quelle per "umani" molto difficile da trovare per mancanza di indicazioni, area cani priva di secchi, fonti di acqua e ombra! - un pò troppe mosche e formiche; Consiglio vivamente di portare scarpette da scoglio per andare al mare specialmente per la spiaggia di ciottoli, una racchetta per uccidere le zanzare e mosche, canavacci per la cucina (non forniti).…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Piscina, Bar/lounge, Noleggio di biciclette, Biciclette disponibili, Area giochi interna per bambini, Attività per bambini/famiglie, Internet, Piscina a sfioro, Piscina per adulti, Piscina all'aperto, Piscina piccola, Piscina recintata, Ristorante, Colazione disponibile, Freccette, Intrattenimento serale, Pesca, Karaoke, Ping pong, Miniclub, Piscina per bambini, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Navetta o servizio taxi gratis, Servizio navetta, Hotel per non fumatori, Angolo cottura, Frigorifero, Utensili da cucina, Camere non fumatori, Camere per famiglie, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.it/Hotel_Review-g2189383-d4923901-Reviews-Centro_Vacanze_Garden_River-Altidona_Province_of_Fermo_Marche.html</t>
-  </si>
-  <si>
-    <t>amapolas-villaggio-&amp;-camping</t>
-  </si>
-  <si>
-    <t>Amapolas Villaggio &amp; Camping</t>
-  </si>
-  <si>
-    <t>225 Via Villagrande, 61024 Mombaroccio Italia</t>
-  </si>
-  <si>
-    <t>Amapolas Villaggio è situato tra le dolci colline di Villagrande di Mombaroccio, punto di partenza ideale per vivere i sapori e i colori delle Marche. A disposizione dei nostri ospiti casette mobili di diverse dimensioni in cui soggiornare nel comfort più totale: dotate di cucina attrezzata, bagno con doccia, aria condizionata e patio con vista sul paesaggio rurale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcheggio gratuito, Animali domestici ammessi, Angolo cottura, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.it/Hotel_Review-g2136886-d21340843-Reviews-Amapolas_Villaggio_Camping-Mombaroccio_Province_of_Pesaro_and_Urbino_Marche.html</t>
-  </si>
-  <si>
-    <t>residence-mare</t>
-  </si>
-  <si>
-    <t>Residence Mare</t>
-  </si>
-  <si>
-    <t>Via Ugo La Malfa 19 Località Lido San Tommaso, 63900, Fermo Italia</t>
-  </si>
-  <si>
-    <t>Il Villaggio Turistico Residence Mare si trova nel centro abitato di Lido San Tommaso sul lungomare nord di Fermo ed è un luogo ideale per famiglie con bambini e coppie poichè è tranquillo, essendo di piccole dimensioni e senza il frastuono stradale o ferroviario. Si trova sulla spiaggia libera alla quale si accede direttamente (senza alcun costo d'ingresso), composta di sabbia e ghiaia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Caffetteria, Noleggio di biciclette, Aerobica, Servizio di babysitter, Parco giochi per bambini, Wi-Fi, Ristorante, Colazione disponibile, Pasti per bambini, Zona pranzo all'aperto, Freccette, Personale di intrattenimento, Intrattenimento serale, Pesca, Karaoke, Ping pong, Attività per bambini/famiglie, Miniclub, Giochi all'aperto per bambini, Seggioloni disponibili, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio taxi, Trattamenti per il viso, Massaggio completo, Manicure, Massaggio, Servizi di ceretta, Accesso diretto alle piste da sci, Sicurezza 24 ore su 24, Area barbecue, Concierge, Hotel per non fumatori, Lettini/sedie sdraio, Ombrelloni, Cassetta di pronto soccorso, Infermeria, Ombrello, Check-in/check-out express, Servizio lavanderia, Lavanderia self-service, Servizio stireria, Purificatore d'aria, Aria condizionata, Servizio di pulizia, Balcone privato, Bagni privati, Angolo cottura, TV satellitare/via cavo, Bidet, Pavimento in piastrelle/marmo, Frigorifero, Piano cottura, Utensili da cucina, TV a schermo piatto, Cabina doccia, Asciugacapelli, Vista sulla piscina, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.it/Hotel_Review-g1025201-d677045-Reviews-Villaggio_Turistico_Residence_Mare-Fermo_Province_of_Fermo_Marche.html</t>
-  </si>
-  <si>
-    <t>camping-villaggio-cortina</t>
-  </si>
-  <si>
-    <t>Lungomare Italia 1/1, 60019, Senigallia Italia</t>
-  </si>
-  <si>
-    <t>Il camping è perfetto per chi viaggia con il proprio cane. Le mobile homes sono molto datate e necessitato di manutenzione ma per chi si adatta vanno bene. Ottimo che siano recintate per permettere ai cani di stare liberi. La spiaggia per cani è a due passi. Il posto è molto tranquillo ma totalmente privo di servizi. Il primo supermercato è a 2km quindi è essenziale che il camping pensi di aprire un minimarket almeno per i prodotti freschi e di base. Il bar è molto scarno. La ferrovia passa a circa 20 metri dalle casette ma personalmente non ci facevo troppo caso. Il campeggio in generale seppur vecchio è pulito. Tornerei perché è una vacanza a misura di cane e all'insegna del relax ma devono necessariamente garantire qualche servizio in più, anche perché spostandosi di pochi chilometri si possono trovare altre bau beach con annessi campeggi molto più vicine ai servizi.…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcheggio gratuito, Con accesso a Internet gratuito, Bar/lounge, Spiaggia, Noleggio di biciclette, Miniclub, Giochi all'aperto per bambini, Animali domestici ammessi, Parcheggio in strada, Ristorante, Pasti per bambini, Snack bar, Personale di intrattenimento, Intrattenimento serale, Ping pong, Servizio navetta, Area barbecue, Minimarket, Hotel per non fumatori, Servizio lavanderia, Aria condizionata, Spiaggia privata, Zona soggiorno, Acqua in bottiglia, Angolo cottura, Frigorifero, Utensili da cucina, TV a schermo piatto, Camere non fumatori, Camere per famiglie, Camere per fumatori disponibili, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.it/Hotel_Review-g194914-d3309922-Reviews-Camping_Villaggio_Cortina-Senigallia_Province_of_Ancona_Marche.html</t>
+    <t>Via Consolazione 20, 60012 Borgo della Consolazione, Trecastelli Italia</t>
+  </si>
+  <si>
+    <t>Casale Civetta ha un parco alberato con sentieri per passeggiate interne interrotte da tavoli in pietra. Ampi spazi aperti, pavimentati con mattoni dove camminare a piedi nudi.Una piscina panoramica sulle colline.Un laboratorio di scultura del tufo.Alberi da frutto. Animali in libertà, pesci, gatti e galline. Amicizia, familiarità,semplicità,arte,accoglienza e condivisione della propria umanità.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcheggio gratuito, Internet ad alta velocità gratuito (WiFi), Piscina, Lezioni di yoga, Bar a bordo piscina, Spiaggia, Noleggio di biciclette, Attività per bambini/famiglie, Parcheggio custodito, Wi-Fi, Teli da piscina/mare, Piscina con vista, Piscina all'aperto, Piscina con estremità bassa, Piscina recintata, Ristorante, Pasti per bambini, Giochi all'aperto per bambini, Animali domestici ammessi, Trasporti per l'aeroporto, Servizio navetta, Sale riunioni, Area barbecue, Deposito bagagli, Hotel per non fumatori, Arredi esterni, Area picnic, Lettini/sedie sdraio, Terrazza solarium, Reception 24 ore su 24, Servizio lavanderia, Acqua in bottiglia, Angolo cottura, Camere per famiglie, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.it/Hotel_Review-g23906399-d12336250-Reviews-Casale_Civetta-Borgo_della_Consolazione_Trecastelli_Province_of_Ancona_Marche.html</t>
+  </si>
+  <si>
+    <t>La Mimosa Camping</t>
+  </si>
+  <si>
+    <t>Strada Nazionale Adriatica Sud 259, 61032, Fano Italy</t>
+  </si>
+  <si>
+    <t>We had booked a holiday cottage to attend a family wedding in the local area. We were so happy that we chose La Mimosa. Our Italian language is not good but they went out of the way to make us feel welcome and looked after.   The chalet was modern, clean, neat and tidy, exactly as advertised. There were basic kitchen utensils to use and the small shop at reception is very convenient. The Chalet is small but functional, perfect for a seaside holiday.  This is a family run business and everybody went out of their way to see that we were welcome and looked after. The seafood restaurant was also excellent.  The beach is easy to get to and ideal for smaller children as there is loads of sand to play on and the water is very shallow. The sun loungers that come with the accommodation booking are lovely to use. Throughout the visit we felt safe and secure.  We found a large supermarket about 6 km (heading south) down the road for more supplies.   I would certainly go there again and have already recommended it to other family members with children.…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Pool, Bar / lounge, Entertainment staff, Children Activities (Kid / Family Friendly), Kids club, Pets Allowed ( Dog / Pet Friendly ), Internet, Outdoor pool, Restaurant, Poolside bar, Convenience store, Air conditioning, Private beach, Kitchenette, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g194759-d4026529-Reviews-La_Mimosa_Camping-Fano_Province_of_Pesaro_and_Urbino_Marche.html</t>
   </si>
   <si>
     <t>la-mimosa-camping</t>
   </si>
   <si>
-    <t>La Mimosa Camping</t>
-  </si>
-  <si>
-    <t>Strada Nazionale Adriatica Sud 259, 61032, Fano Italy</t>
-  </si>
-  <si>
-    <t>We had booked a holiday cottage to attend a family wedding in the local area. We were so happy that we chose La Mimosa. Our Italian language is not good but they went out of the way to make us feel welcome and looked after.   The chalet was modern, clean, neat and tidy, exactly as advertised. There were basic kitchen utensils to use and the small shop at reception is very convenient. The Chalet is small but functional, perfect for a seaside holiday.  This is a family run business and everybody went out of their way to see that we were welcome and looked after. The seafood restaurant was also excellent.  The beach is easy to get to and ideal for smaller children as there is loads of sand to play on and the water is very shallow. The sun loungers that come with the accommodation booking are lovely to use. Throughout the visit we felt safe and secure.  We found a large supermarket about 6 km (heading south) down the road for more supplies.   I would certainly go there again and have already recommended it to other family members with children.…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Pool, Bar / lounge, Entertainment staff, Children Activities (Kid / Family Friendly), Kids club, Pets Allowed ( Dog / Pet Friendly ), Internet, Outdoor pool, Restaurant, Poolside bar, Convenience store, Air conditioning, Private beach, Kitchenette, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g194759-d4026529-Reviews-La_Mimosa_Camping-Fano_Province_of_Pesaro_and_Urbino_Marche.html</t>
+    <t>Camping Vettore</t>
+  </si>
+  <si>
+    <t>Strada Per San Nicola 15, 63094, Montegallo Italy</t>
+  </si>
+  <si>
+    <t>This is the best camping that I have ever been to in my entire life! This is absolute fantastic place to be with Your tent. The lovely scenery and quiet enviorement is just welcoming here and making You want to stay there for days! A tent-perfect-place to stay: green clean grass, good showers and bath facilities. The village is very close with two shops, couple restourants and cafes. The mountain trails are very close so this is the ultimate camping site in Apennines. Very quiet and cheap.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Restaurant, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Kitchenette, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g2002511-d2318786-Reviews-Camping_Vettore-Montegallo_Province_of_Ascoli_Piceno_Marche.html</t>
   </si>
   <si>
     <t>camping-vettore</t>
   </si>
   <si>
-    <t>Camping Vettore</t>
-  </si>
-  <si>
-    <t>Strada Per San Nicola 15, 63094, Montegallo Italy</t>
-  </si>
-  <si>
-    <t>This is the best camping that I have ever been to in my entire life! This is absolute fantastic place to be with Your tent. The lovely scenery and quiet enviorement is just welcoming here and making You want to stay there for days! A tent-perfect-place to stay: green clean grass, good showers and bath facilities. The village is very close with two shops, couple restourants and cafes. The mountain trails are very close so this is the ultimate camping site in Apennines. Very quiet and cheap.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Restaurant, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Kitchenette, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g2002511-d2318786-Reviews-Camping_Vettore-Montegallo_Province_of_Ascoli_Piceno_Marche.html</t>
+    <t>Camping Monte Prata</t>
+  </si>
+  <si>
+    <t>Localita Schianceto SNC, 62039, Castelsantangelo sul Nera Italy</t>
+  </si>
+  <si>
+    <t>Spacious pitches, lots of shade, remote pitches where you can enjoy the silence and the sounds of nature. The location is beautiful, we have heard wolves, boar, owls, hawks and an eagle, seen squirrels and a wild cat all from our pitch. During our visit two staff members played acoustic guitar(rock) from time to time, for us it really added to the atmosphere. The staff is friendly and helpful, there is a really nice bar-market(though a bit small).  The price is good. The sanitary is a bit outdated, but it works.  The nearest supermarket is ca. 35mins drive away in Borgo Ceretto(Eurospin franchise). The camping lays at +1200 m above sealevel, this means it can get a bit cold after sundown(I only brought one sweater, really should've brought more).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pets Allowed ( Dog / Pet Friendly ), </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g1566582-d3310023-Reviews-Camping_Monte_Prata-Castelsantangelo_sul_Nera_Province_of_Macerata_Marche.html</t>
   </si>
   <si>
     <t>camping-monte-prata</t>
   </si>
   <si>
-    <t>Camping Monte Prata</t>
-  </si>
-  <si>
-    <t>Localita Schianceto SNC, 62039, Castelsantangelo sul Nera Italy</t>
-  </si>
-  <si>
-    <t>Spacious pitches, lots of shade, remote pitches where you can enjoy the silence and the sounds of nature. The location is beautiful, we have heard wolves, boar, owls, hawks and an eagle, seen squirrels and a wild cat all from our pitch. During our visit two staff members played acoustic guitar(rock) from time to time, for us it really added to the atmosphere. The staff is friendly and helpful, there is a really nice bar-market(though a bit small).  The price is good. The sanitary is a bit outdated, but it works.  The nearest supermarket is ca. 35mins drive away in Borgo Ceretto(Eurospin franchise). The camping lays at +1200 m above sealevel, this means it can get a bit cold after sundown(I only brought one sweater, really should've brought more).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pets Allowed ( Dog / Pet Friendly ), </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g1566582-d3310023-Reviews-Camping_Monte_Prata-Castelsantangelo_sul_Nera_Province_of_Macerata_Marche.html</t>
+    <t>Camping Centro Turistico Belvedere</t>
+  </si>
+  <si>
+    <t>Montecucco 19, 62012, Civitanova Marche Italy</t>
+  </si>
+  <si>
+    <t>Camping Centro Turistico Belvedere is located in Civitanova Marche, at less than 1 km from the sea. Placed on the top of a hill completely covered by a pine forest, it offers a beautiful panorama from Monte Conero to San Benedetto. Camping places are completely shady; you can also rent caravans or bungalows. Moreover, Camping Belvedere offers two swimming pools, a coffee bar, a restaurant and a pizzeria. Dogs and other pets welcome!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Pool, Bar / lounge, Restaurant, Breakfast available, Tennis court, Pets Allowed ( Dog / Pet Friendly ), Self-serve laundry, Refrigerator, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g194742-d1993072-Reviews-Camping_Centro_Turistico_Belvedere-Civitanova_Marche_Province_of_Macerata_Marche.html</t>
   </si>
   <si>
     <t>camping-centro-turistico-belvedere</t>
   </si>
   <si>
-    <t>Camping Centro Turistico Belvedere</t>
-  </si>
-  <si>
-    <t>Montecucco 19, 62012, Civitanova Marche Italy</t>
-  </si>
-  <si>
-    <t>Camping Centro Turistico Belvedere is located in Civitanova Marche, at less than 1 km from the sea. Placed on the top of a hill completely covered by a pine forest, it offers a beautiful panorama from Monte Conero to San Benedetto. Camping places are completely shady; you can also rent caravans or bungalows. Moreover, Camping Belvedere offers two swimming pools, a coffee bar, a restaurant and a pizzeria. Dogs and other pets welcome!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Pool, Bar / lounge, Restaurant, Breakfast available, Tennis court, Pets Allowed ( Dog / Pet Friendly ), Self-serve laundry, Refrigerator, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g194742-d1993072-Reviews-Camping_Centro_Turistico_Belvedere-Civitanova_Marche_Province_of_Macerata_Marche.html</t>
+    <t>Camping Stella Maris</t>
+  </si>
+  <si>
+    <t>Via Ammiraglio Cappellini 5, 61032, Fano Italy</t>
+  </si>
+  <si>
+    <t>Super camping. Evwrything is relaxed. Very nice beach and perfect swimmingpool. The son of the owner is the sweetest person in the world. He suprised us with a pick up with a very nice car to bring us to an excellent restaurant. If you look for a perfect camping this is the one!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Beach, Children Activities (Kid / Family Friendly), Kids club, Pets Allowed ( Dog / Pet Friendly ), Restaurant, Swimup bar, Kitchenette, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g194759-d6603161-Reviews-Camping_Stella_Maris-Fano_Province_of_Pesaro_and_Urbino_Marche.html</t>
   </si>
   <si>
     <t>camping-stella-maris</t>
   </si>
   <si>
-    <t>Camping Stella Maris</t>
-  </si>
-  <si>
-    <t>Via Ammiraglio Cappellini 5, 61032, Fano Italy</t>
-  </si>
-  <si>
-    <t>Super camping. Evwrything is relaxed. Very nice beach and perfect swimmingpool. The son of the owner is the sweetest person in the world. He suprised us with a pick up with a very nice car to bring us to an excellent restaurant. If you look for a perfect camping this is the one!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Beach, Children Activities (Kid / Family Friendly), Kids club, Pets Allowed ( Dog / Pet Friendly ), Restaurant, Swimup bar, Kitchenette, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g194759-d6603161-Reviews-Camping_Stella_Maris-Fano_Province_of_Pesaro_and_Urbino_Marche.html</t>
+    <t>Conero Azzurro</t>
+  </si>
+  <si>
+    <t>Via Castelfidardo 80, 60026 Numana Italy</t>
+  </si>
+  <si>
+    <t>Villaggio immerso nel verde, con cottage, chalet e bungalow indipendenti. Situato in prima fila mare, con ampia spiaggia privata e accesso diretto tramite un comodo sottopasso. Ideale per famiglie con bambini.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Beach, Bicycle rental, Children Activities (Kid / Family Friendly), Kids club, Wifi, Outdoor pool, Plunge pool, Restaurant, Breakfast available, Kids' meals, Snack bar, Swimup bar, Tennis court, Entertainment staff, Table tennis, Kids' outdoor play equipment, Conference facilities, Banquet room, Meeting rooms, Convenience store, Gift shop, Sun umbrellas, Self-serve laundry, Air conditioning, Private beach, Safe, Kitchenette, Refrigerator, Non-smoking rooms, Family rooms, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g194838-d676423-Reviews-Conero_Azzurro-Numana_Province_of_Ancona_Marche.html</t>
   </si>
   <si>
     <t>conero-azzurro</t>
   </si>
   <si>
-    <t>Conero Azzurro</t>
-  </si>
-  <si>
-    <t>Via Castelfidardo 80, 60026 Numana Italy</t>
-  </si>
-  <si>
-    <t>Villaggio immerso nel verde, con cottage, chalet e bungalow indipendenti. Situato in prima fila mare, con ampia spiaggia privata e accesso diretto tramite un comodo sottopasso. Ideale per famiglie con bambini.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Beach, Bicycle rental, Children Activities (Kid / Family Friendly), Kids club, Wifi, Outdoor pool, Plunge pool, Restaurant, Breakfast available, Kids' meals, Snack bar, Swimup bar, Tennis court, Entertainment staff, Table tennis, Kids' outdoor play equipment, Conference facilities, Banquet room, Meeting rooms, Convenience store, Gift shop, Sun umbrellas, Self-serve laundry, Air conditioning, Private beach, Safe, Kitchenette, Refrigerator, Non-smoking rooms, Family rooms, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g194838-d676423-Reviews-Conero_Azzurro-Numana_Province_of_Ancona_Marche.html</t>
+    <t>Camping Don Diego</t>
+  </si>
+  <si>
+    <t>Lungomare Alcide De' Gasperi 128, 63066 Grottammare Italy</t>
+  </si>
+  <si>
+    <t>Village and Camping on the sea of the Riviera of the Palms, in the Region Marche, central Italy, adriatic coast. Bungalows in masonry and pitche for camping open air, at 10 mt from the sea by shallow water and fine sand. Clean sea by European Blue Flag.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Bar / lounge, Beach, Children Activities (Kid / Family Friendly), Kids club, Business Center with Internet Access, Self-serve laundry, Wifi, Restaurant, Kitchenette, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g730082-d1548649-Reviews-Camping_Don_Diego-Grottammare_Province_of_Ascoli_Piceno_Marche.html</t>
   </si>
   <si>
     <t>camping-don-diego</t>
   </si>
   <si>
-    <t>Camping Don Diego</t>
-  </si>
-  <si>
-    <t>Lungomare Alcide De' Gasperi 128, 63066 Grottammare Italy</t>
-  </si>
-  <si>
-    <t>Village and Camping on the sea of the Riviera of the Palms, in the Region Marche, central Italy, adriatic coast. Bungalows in masonry and pitche for camping open air, at 10 mt from the sea by shallow water and fine sand. Clean sea by European Blue Flag.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Bar / lounge, Beach, Children Activities (Kid / Family Friendly), Kids club, Business Center with Internet Access, Self-serve laundry, Wifi, Restaurant, Kitchenette, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g730082-d1548649-Reviews-Camping_Don_Diego-Grottammare_Province_of_Ascoli_Piceno_Marche.html</t>
+    <t>Camping Lpre</t>
+  </si>
+  <si>
+    <t>Via Giacomo Matteotti 45, 60010 Ostra Italy</t>
+  </si>
+  <si>
+    <t>Campeggio nella campagna dell'entroterra marchigiano (tra i caselli autostradali di Senigallia e Montemarciano-15/20 min.) situato in borgo tranquillo e caratteristico. Piazzole ampie e ombreggiate da ulivi, servizi igienici pulitissimi. Titolare (e fidanzata) molto gentili e accoglienti. Ottima copertura wifi gratuito in tutta la struttura. Torneremo presto a trovarvi: complimenti e grazie di tutto!!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free High Speed Internet (WiFi), Wifi, Pets Allowed ( Dog / Pet Friendly ), </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g2140648-d3519310-Reviews-Camping_Lpre-Ostra_Province_of_Ancona_Marche.html</t>
   </si>
   <si>
     <t>camping-lpre</t>
   </si>
   <si>
-    <t>Camping Lpre</t>
-  </si>
-  <si>
-    <t>Via Giacomo Matteotti 45, 60010 Ostra Italy</t>
-  </si>
-  <si>
-    <t>Campeggio nella campagna dell'entroterra marchigiano (tra i caselli autostradali di Senigallia e Montemarciano-15/20 min.) situato in borgo tranquillo e caratteristico. Piazzole ampie e ombreggiate da ulivi, servizi igienici pulitissimi. Titolare (e fidanzata) molto gentili e accoglienti. Ottima copertura wifi gratuito in tutta la struttura. Torneremo presto a trovarvi: complimenti e grazie di tutto!!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free High Speed Internet (WiFi), Wifi, Pets Allowed ( Dog / Pet Friendly ), </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g2140648-d3519310-Reviews-Camping_Lpre-Ostra_Province_of_Ancona_Marche.html</t>
+    <t>Camping Bellamare</t>
+  </si>
+  <si>
+    <t>Viale Scarfiotti 13, 62017 Porto Recanati Italy</t>
+  </si>
+  <si>
+    <t>The Bellamare Camping is immersed in the enchanting Conero Riviera covering an area of 50,000 sq mt. It is the perfect starting point for excursions and visits to places of major touristic interest in the Marche. The Camping Bellamare is directly by the beach of Porto Recanati far away from the railway, which is quite an exceptional location along the Adriatic coast of Marche. The campsite offers various types of accommodations such as pleasant bungalows, beachfront apartments and finely curated lown grass pitches each one surrounded by trees. The entetainment team of the campsite organizes fun activities, games, kids club, evening shows, sports for adults and kids. Porto Recanati is an oasis of peace and tranquility in the beautiful scenery of Mount Conero, the ideal place for your holiday in the Marche.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Free internet, Pool, Fitness classes, Bar / lounge, Beach, Bicycle rental, Children's playground, Wifi, Paid wifi, Adult pool, Outdoor pool, Plunge pool, Shallow end in pool, Coffee shop, Restaurant, Breakfast available, Outdoor dining area, Snack bar, Wine / champagne, Swimup bar, Poolside bar, Game room, Hiking, Aerobics, Entertainment staff, Evening entertainment, Indoor play area for children, Children Activities (Kid / Family Friendly), Kids club, Kids' outdoor play equipment, Highchairs available, Concierge, Convenience store, Sun deck, Sun loungers / beach chairs, Sun terrace, Sun umbrellas, Infirmary, Express check-in / check-out, Clothes dryer, Laundry service, Self-serve laundry, Washing machine, Allergy-free room, Air conditioning, Dining area, Housekeeping, Clothes rack, Microwave, Stovetop, Walk-in shower, Kitchenware, Hair dryer, Family rooms, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g194858-d1815916-Reviews-Camping_Bellamare-Porto_Recanati_Province_of_Macerata_Marche.html</t>
   </si>
   <si>
     <t>camping-bellamare</t>
   </si>
   <si>
-    <t>Camping Bellamare</t>
-  </si>
-  <si>
-    <t>Viale Scarfiotti 13, 62017 Porto Recanati Italy</t>
-  </si>
-  <si>
-    <t>The Bellamare Camping is immersed in the enchanting Conero Riviera covering an area of 50,000 sq mt. It is the perfect starting point for excursions and visits to places of major touristic interest in the Marche. The Camping Bellamare is directly by the beach of Porto Recanati far away from the railway, which is quite an exceptional location along the Adriatic coast of Marche. The campsite offers various types of accommodations such as pleasant bungalows, beachfront apartments and finely curated lown grass pitches each one surrounded by trees. The entetainment team of the campsite organizes fun activities, games, kids club, evening shows, sports for adults and kids. Porto Recanati is an oasis of peace and tranquility in the beautiful scenery of Mount Conero, the ideal place for your holiday in the Marche.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Free internet, Pool, Fitness classes, Bar / lounge, Beach, Bicycle rental, Children's playground, Wifi, Paid wifi, Adult pool, Outdoor pool, Plunge pool, Shallow end in pool, Coffee shop, Restaurant, Breakfast available, Outdoor dining area, Snack bar, Wine / champagne, Swimup bar, Poolside bar, Game room, Hiking, Aerobics, Entertainment staff, Evening entertainment, Indoor play area for children, Children Activities (Kid / Family Friendly), Kids club, Kids' outdoor play equipment, Highchairs available, Concierge, Convenience store, Sun deck, Sun loungers / beach chairs, Sun terrace, Sun umbrellas, Infirmary, Express check-in / check-out, Clothes dryer, Laundry service, Self-serve laundry, Washing machine, Allergy-free room, Air conditioning, Dining area, Housekeeping, Clothes rack, Microwave, Stovetop, Walk-in shower, Kitchenware, Hair dryer, Family rooms, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g194858-d1815916-Reviews-Camping_Bellamare-Porto_Recanati_Province_of_Macerata_Marche.html</t>
+    <t>Camping Reno</t>
+  </si>
+  <si>
+    <t>Via Moricone 7, 60020 Sirolo Italy</t>
+  </si>
+  <si>
+    <t>The location of this campsite is excellent, although on a steep hill, it is possible to walk into the centre of the beautiful town in 10 minutes.   The campsite is very basic with fairly poor, unrenovated sanitaire.  Staff are very pleasant and helpful.  Sirolo is worth a visit, and has great views over the sea.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bar / lounge, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Kitchenette, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g608900-d4817085-Reviews-Camping_Reno-Sirolo_Province_of_Ancona_Marche.html</t>
   </si>
   <si>
     <t>camping-reno</t>
   </si>
   <si>
-    <t>Camping Reno</t>
-  </si>
-  <si>
-    <t>Via Moricone 7, 60020 Sirolo Italy</t>
-  </si>
-  <si>
-    <t>The location of this campsite is excellent, although on a steep hill, it is possible to walk into the centre of the beautiful town in 10 minutes.   The campsite is very basic with fairly poor, unrenovated sanitaire.  Staff are very pleasant and helpful.  Sirolo is worth a visit, and has great views over the sea.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bar / lounge, Children Activities (Kid / Family Friendly), Pets Allowed ( Dog / Pet Friendly ), Kitchenette, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g608900-d4817085-Reviews-Camping_Reno-Sirolo_Province_of_Ancona_Marche.html</t>
+    <t>Camping Summerland</t>
+  </si>
+  <si>
+    <t>Via Francesco Podesti 236, 60019, Senigallia Italy</t>
+  </si>
+  <si>
+    <t>The Camping Holiday Center Summerland rises in a quiet and shady area within the residential zone of Senigallia. The so-called "Spiaggia di Velluto" (“Velvet beach”), famous for its wonderful sandy beach, is only 150 m. far from the camping. It’s the ideal place for children because of the knee-deep water; tourists can choose between free beach (free access) or private beach (with beach facilities on charge). The camping extends on a 45.000 square meters area of grassy ground and has: 176 little squares, 89 bungalows, 10 chalets, 3 restrooms located in different areas with free hot water in showers and washbasins (no coins!!!), two inside parking places and an outside one. Our strong points are the green areas, 3 swimming pools with solarium and sports facilities (soccer and volley grounds, tennis court) all free-access. A friendly staff will welcome you at the camping. We work for families from more than 40 years; for that reason we can satisfy both adults and children needs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Pool, Bar / lounge, Tennis court, Entertainment staff, Children Activities (Kid / Family Friendly), Kids club, Wifi, Outdoor pool, Restaurant, Evening entertainment, Kids' outdoor play equipment, Pets Allowed ( Dog / Pet Friendly ), Concierge, Convenience store, Laundry service, Self-serve laundry, Air conditioning, Kitchenette, Microwave, Refrigerator, Family rooms, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g194914-d2316135-Reviews-Camping_Summerland-Senigallia_Province_of_Ancona_Marche.html</t>
   </si>
   <si>
     <t>camping-summerland</t>
   </si>
   <si>
-    <t>Camping Summerland</t>
-  </si>
-  <si>
-    <t>Via Francesco Podesti 236, 60019, Senigallia Italy</t>
-  </si>
-  <si>
-    <t>The Camping Holiday Center Summerland rises in a quiet and shady area within the residential zone of Senigallia. The so-called "Spiaggia di Velluto" (“Velvet beach”), famous for its wonderful sandy beach, is only 150 m. far from the camping. It’s the ideal place for children because of the knee-deep water; tourists can choose between free beach (free access) or private beach (with beach facilities on charge). The camping extends on a 45.000 square meters area of grassy ground and has: 176 little squares, 89 bungalows, 10 chalets, 3 restrooms located in different areas with free hot water in showers and washbasins (no coins!!!), two inside parking places and an outside one. Our strong points are the green areas, 3 swimming pools with solarium and sports facilities (soccer and volley grounds, tennis court) all free-access. A friendly staff will welcome you at the camping. We work for families from more than 40 years; for that reason we can satisfy both adults and children needs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Pool, Bar / lounge, Tennis court, Entertainment staff, Children Activities (Kid / Family Friendly), Kids club, Wifi, Outdoor pool, Restaurant, Evening entertainment, Kids' outdoor play equipment, Pets Allowed ( Dog / Pet Friendly ), Concierge, Convenience store, Laundry service, Self-serve laundry, Air conditioning, Kitchenette, Microwave, Refrigerator, Family rooms, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g194914-d2316135-Reviews-Camping_Summerland-Senigallia_Province_of_Ancona_Marche.html</t>
+    <t>Camping Gabicce Monte</t>
+  </si>
+  <si>
+    <t>Via Panoramica 148, 61011 Gabicce Monte Italy</t>
+  </si>
+  <si>
+    <t>Camping Gabicce Monte is a small and intimate camp, surrounded by the San Bartolo natural park. A cool and shaded terrace overlooking the sea from which to enjoy a beautiful landscape. Located halfway between the sea and Gabicce Vallugola, Camping Gabicce Monte is perfect for lovers of hiking or biking. The beaches of Gabicce and Cattolica are easily reachable on foot in 15 minutes through scenic trails. The bay cobbled below the campground is instead reached in about ten minutes through a path in the wild and enchanting forest. From the rooftop terrace of Gabicce Monte, just 500 meters from the campsite, there are buses and shuttles every half hour to the beaches. Finally, for the very young or the nightlife lovers, the campsite is just a few minutes by car or on foot from bar and pubs of Gabicce and Cattolica and one of the most famous discos of the Riviera: the Baia Imperiale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Wifi, Breakfast available, Pets Allowed ( Dog / Pet Friendly ), BBQ facilities, Concierge, Self-serve laundry, Non-smoking hotel, Air conditioning, Kitchenette, Refrigerator, Ocean view, Non-smoking rooms, Family rooms, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g2275905-d2250335-Reviews-Camping_Gabicce_Monte-Gabicce_Monte_Province_of_Pesaro_and_Urbino_Marche.html</t>
   </si>
   <si>
     <t>camping-gabicce-monte</t>
   </si>
   <si>
-    <t>Camping Gabicce Monte</t>
-  </si>
-  <si>
-    <t>Via Panoramica 148, 61011 Gabicce Monte Italy</t>
-  </si>
-  <si>
-    <t>Camping Gabicce Monte is a small and intimate camp, surrounded by the San Bartolo natural park. A cool and shaded terrace overlooking the sea from which to enjoy a beautiful landscape. Located halfway between the sea and Gabicce Vallugola, Camping Gabicce Monte is perfect for lovers of hiking or biking. The beaches of Gabicce and Cattolica are easily reachable on foot in 15 minutes through scenic trails. The bay cobbled below the campground is instead reached in about ten minutes through a path in the wild and enchanting forest. From the rooftop terrace of Gabicce Monte, just 500 meters from the campsite, there are buses and shuttles every half hour to the beaches. Finally, for the very young or the nightlife lovers, the campsite is just a few minutes by car or on foot from bar and pubs of Gabicce and Cattolica and one of the most famous discos of the Riviera: the Baia Imperiale.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Free High Speed Internet (WiFi), Wifi, Breakfast available, Pets Allowed ( Dog / Pet Friendly ), BBQ facilities, Concierge, Self-serve laundry, Non-smoking hotel, Air conditioning, Kitchenette, Refrigerator, Ocean view, Non-smoking rooms, Family rooms, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g2275905-d2250335-Reviews-Camping_Gabicce_Monte-Gabicce_Monte_Province_of_Pesaro_and_Urbino_Marche.html</t>
+    <t>Camping Club Internazionale</t>
+  </si>
+  <si>
+    <t>Via San Michele 10, 60020 Sirolo Italy</t>
+  </si>
+  <si>
+    <t>The site is beautiful, servise is nice, food is good in restaurant, good choice in the shop, clean bathrooms, short walk to the beach and downtown. While the quite hours are respected within the camping itself it is of no use at all, because of the noise from Sirolo till late night. Everynight. Is like your tent is placed in some bar. Was tired everyday we stayed in the camping. This canceled all the good points the camping offers, i did not enjoy my stay at all and do not advice for anyone who cant sleep in noisy places.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Bicycle rental, Table tennis, Books, DVDs, music for children, Children Activities (Kid / Family Friendly), Wifi, Paid wifi, Outdoor pool, Shallow end in pool, Fence around pool, Restaurant, Special diet menus, Vending machine, Tennis court offsite, Kids club, Kids' outdoor play equipment, BBQ facilities, Concierge, Convenience store, Newspaper, Outdoor furniture, Picnic area, Sun loungers / beach chairs, Sun terrace, Self-serve laundry, Ocean view, </t>
+  </si>
+  <si>
+    <t>https://www.tripadvisor.com/Hotel_Review-g608900-d1520372-Reviews-Camping_Club_Internazionale-Sirolo_Province_of_Ancona_Marche.html</t>
   </si>
   <si>
     <t>camping-club-internazionale</t>
-  </si>
-  <si>
-    <t>Camping Club Internazionale</t>
-  </si>
-  <si>
-    <t>Via San Michele 10, 60020 Sirolo Italy</t>
-  </si>
-  <si>
-    <t>The site is beautiful, servise is nice, food is good in restaurant, good choice in the shop, clean bathrooms, short walk to the beach and downtown. While the quite hours are respected within the camping itself it is of no use at all, because of the noise from Sirolo till late night. Everynight. Is like your tent is placed in some bar. Was tired everyday we stayed in the camping. This canceled all the good points the camping offers, i did not enjoy my stay at all and do not advice for anyone who cant sleep in noisy places.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free parking, Free internet, Pool, Bar / lounge, Bicycle rental, Table tennis, Books, DVDs, music for children, Children Activities (Kid / Family Friendly), Wifi, Paid wifi, Outdoor pool, Shallow end in pool, Fence around pool, Restaurant, Special diet menus, Vending machine, Tennis court offsite, Kids club, Kids' outdoor play equipment, BBQ facilities, Concierge, Convenience store, Newspaper, Outdoor furniture, Picnic area, Sun loungers / beach chairs, Sun terrace, Self-serve laundry, Ocean view, </t>
-  </si>
-  <si>
-    <t>https://www.tripadvisor.com/Hotel_Review-g608900-d1520372-Reviews-Camping_Club_Internazionale-Sirolo_Province_of_Ancona_Marche.html</t>
-  </si>
-  <si>
-    <t>la-bolla-del-borgo-le-marche-tra-le-stelle</t>
   </si>
 </sst>
 </file>
@@ -1549,16 +1543,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" customWidth="1"/>
-    <col min="5" max="5" width="25.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="38.28515625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="39.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -1680,22 +1669,22 @@
         <v>32</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="J4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N4" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1747,7 +1736,7 @@
         <v>49</v>
       </c>
       <c r="H6" t="s">
-        <v>322</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1755,25 +1744,25 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1781,25 +1770,25 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1807,25 +1796,25 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1833,25 +1822,25 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -1859,25 +1848,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1885,25 +1874,25 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1911,43 +1900,43 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I13" t="s">
+        <v>239</v>
+      </c>
+      <c r="J13" t="s">
+        <v>240</v>
+      </c>
+      <c r="K13" t="s">
+        <v>118</v>
+      </c>
+      <c r="L13" t="s">
+        <v>241</v>
+      </c>
+      <c r="M13" t="s">
+        <v>242</v>
+      </c>
+      <c r="N13" t="s">
         <v>96</v>
-      </c>
-      <c r="J13" t="s">
-        <v>97</v>
-      </c>
-      <c r="K13" t="s">
-        <v>98</v>
-      </c>
-      <c r="L13" t="s">
-        <v>99</v>
-      </c>
-      <c r="M13" t="s">
-        <v>100</v>
-      </c>
-      <c r="N13" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -1955,25 +1944,25 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="H14" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1981,25 +1970,25 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" t="s">
+        <v>107</v>
+      </c>
+      <c r="G15" t="s">
         <v>108</v>
       </c>
-      <c r="C15" t="s">
+      <c r="H15" t="s">
         <v>109</v>
-      </c>
-      <c r="D15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E15" t="s">
-        <v>111</v>
-      </c>
-      <c r="F15" t="s">
-        <v>112</v>
-      </c>
-      <c r="G15" t="s">
-        <v>113</v>
-      </c>
-      <c r="H15" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -2007,43 +1996,43 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D16" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
       </c>
       <c r="F16" t="s">
+        <v>113</v>
+      </c>
+      <c r="G16" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" t="s">
+        <v>115</v>
+      </c>
+      <c r="I16" t="s">
+        <v>116</v>
+      </c>
+      <c r="J16" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" t="s">
         <v>118</v>
       </c>
-      <c r="G16" t="s">
+      <c r="L16" t="s">
         <v>119</v>
       </c>
-      <c r="H16" t="s">
+      <c r="M16" t="s">
         <v>120</v>
       </c>
-      <c r="I16" t="s">
+      <c r="N16" t="s">
         <v>115</v>
-      </c>
-      <c r="J16" t="s">
-        <v>121</v>
-      </c>
-      <c r="K16" t="s">
-        <v>122</v>
-      </c>
-      <c r="L16" t="s">
-        <v>99</v>
-      </c>
-      <c r="M16" t="s">
-        <v>123</v>
-      </c>
-      <c r="N16" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -2051,25 +2040,25 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G17" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -2077,25 +2066,43 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D18" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
       </c>
       <c r="F18" t="s">
+        <v>130</v>
+      </c>
+      <c r="G18" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" t="s">
+        <v>132</v>
+      </c>
+      <c r="I18" t="s">
+        <v>133</v>
+      </c>
+      <c r="J18" t="s">
         <v>134</v>
       </c>
-      <c r="G18" t="s">
+      <c r="K18" t="s">
+        <v>118</v>
+      </c>
+      <c r="L18" t="s">
         <v>135</v>
       </c>
-      <c r="H18" t="s">
+      <c r="M18" t="s">
         <v>136</v>
+      </c>
+      <c r="N18" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -2103,25 +2110,25 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D19" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
         <v>16</v>
       </c>
       <c r="F19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G19" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H19" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -2129,25 +2136,25 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -2155,25 +2162,25 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
       </c>
       <c r="F21" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G21" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H21" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -2181,43 +2188,43 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C22" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E22" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F22" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G22" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H22" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I22" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J22" t="s">
+        <v>164</v>
+      </c>
+      <c r="K22" t="s">
+        <v>118</v>
+      </c>
+      <c r="L22" t="s">
+        <v>165</v>
+      </c>
+      <c r="M22" t="s">
+        <v>166</v>
+      </c>
+      <c r="N22" t="s">
         <v>162</v>
-      </c>
-      <c r="K22" t="s">
-        <v>163</v>
-      </c>
-      <c r="L22" t="s">
-        <v>99</v>
-      </c>
-      <c r="M22" t="s">
-        <v>164</v>
-      </c>
-      <c r="N22" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -2225,25 +2232,25 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D23" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -2251,25 +2258,25 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F24" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -2277,25 +2284,25 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C25" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D25" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E25" t="s">
         <v>16</v>
       </c>
       <c r="F25" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G25" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H25" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2303,586 +2310,560 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D26" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F26" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H26" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I26" t="s">
+        <v>236</v>
+      </c>
+      <c r="J26" t="s">
+        <v>237</v>
+      </c>
+      <c r="K26" t="s">
+        <v>118</v>
+      </c>
+      <c r="M26" t="s">
+        <v>238</v>
+      </c>
+      <c r="N26" t="s">
         <v>192</v>
-      </c>
-      <c r="J26" t="s">
-        <v>193</v>
-      </c>
-      <c r="K26" t="s">
-        <v>194</v>
-      </c>
-      <c r="L26" t="s">
-        <v>99</v>
-      </c>
-      <c r="N26" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="H27" t="s">
+      <c r="B27" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" t="s">
+        <v>194</v>
+      </c>
+      <c r="J27" t="s">
+        <v>195</v>
+      </c>
+      <c r="K27" t="s">
+        <v>118</v>
+      </c>
+      <c r="L27" t="s">
         <v>196</v>
       </c>
-      <c r="I27" t="s">
+      <c r="M27" t="s">
         <v>197</v>
       </c>
-      <c r="J27" t="s">
+      <c r="N27" t="s">
         <v>198</v>
-      </c>
-      <c r="K27" t="s">
-        <v>199</v>
-      </c>
-      <c r="L27" t="s">
-        <v>99</v>
-      </c>
-      <c r="M27" t="s">
-        <v>200</v>
-      </c>
-      <c r="N27" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="H28" t="s">
+      <c r="B28" t="s">
+        <v>199</v>
+      </c>
+      <c r="I28" t="s">
+        <v>200</v>
+      </c>
+      <c r="J28" t="s">
+        <v>201</v>
+      </c>
+      <c r="K28" t="s">
+        <v>118</v>
+      </c>
+      <c r="L28" t="s">
         <v>202</v>
       </c>
-      <c r="I28" t="s">
+      <c r="M28" t="s">
         <v>203</v>
       </c>
-      <c r="J28" t="s">
+      <c r="N28" t="s">
         <v>204</v>
-      </c>
-      <c r="K28" t="s">
-        <v>205</v>
-      </c>
-      <c r="L28" t="s">
-        <v>99</v>
-      </c>
-      <c r="M28" t="s">
-        <v>206</v>
-      </c>
-      <c r="N28" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="H29" t="s">
+      <c r="B29" t="s">
+        <v>205</v>
+      </c>
+      <c r="I29" t="s">
+        <v>206</v>
+      </c>
+      <c r="J29" t="s">
+        <v>207</v>
+      </c>
+      <c r="K29" t="s">
         <v>208</v>
       </c>
-      <c r="I29" t="s">
+      <c r="L29" t="s">
         <v>209</v>
       </c>
-      <c r="J29" t="s">
+      <c r="M29" t="s">
         <v>210</v>
       </c>
-      <c r="K29" t="s">
+      <c r="N29" t="s">
         <v>211</v>
-      </c>
-      <c r="L29" t="s">
-        <v>212</v>
-      </c>
-      <c r="M29" t="s">
-        <v>213</v>
-      </c>
-      <c r="N29" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="H30" t="s">
+      <c r="B30" t="s">
+        <v>212</v>
+      </c>
+      <c r="I30" t="s">
+        <v>213</v>
+      </c>
+      <c r="J30" t="s">
+        <v>214</v>
+      </c>
+      <c r="K30" t="s">
+        <v>118</v>
+      </c>
+      <c r="L30" t="s">
         <v>215</v>
       </c>
-      <c r="I30" t="s">
+      <c r="M30" t="s">
         <v>216</v>
       </c>
-      <c r="J30" t="s">
+      <c r="N30" t="s">
         <v>217</v>
-      </c>
-      <c r="K30" t="s">
-        <v>218</v>
-      </c>
-      <c r="L30" t="s">
-        <v>99</v>
-      </c>
-      <c r="M30" t="s">
-        <v>219</v>
-      </c>
-      <c r="N30" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="H31" t="s">
+      <c r="B31" t="s">
+        <v>218</v>
+      </c>
+      <c r="I31" t="s">
+        <v>219</v>
+      </c>
+      <c r="J31" t="s">
+        <v>220</v>
+      </c>
+      <c r="K31" t="s">
+        <v>118</v>
+      </c>
+      <c r="L31" t="s">
         <v>221</v>
       </c>
-      <c r="I31" t="s">
+      <c r="M31" t="s">
         <v>222</v>
       </c>
-      <c r="J31" t="s">
+      <c r="N31" t="s">
         <v>223</v>
-      </c>
-      <c r="K31" t="s">
-        <v>224</v>
-      </c>
-      <c r="L31" t="s">
-        <v>99</v>
-      </c>
-      <c r="M31" t="s">
-        <v>225</v>
-      </c>
-      <c r="N31" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="H32" t="s">
+      <c r="B32" t="s">
+        <v>224</v>
+      </c>
+      <c r="I32" t="s">
+        <v>225</v>
+      </c>
+      <c r="J32" t="s">
+        <v>226</v>
+      </c>
+      <c r="K32" t="s">
+        <v>118</v>
+      </c>
+      <c r="L32" t="s">
         <v>227</v>
       </c>
-      <c r="I32" t="s">
+      <c r="M32" t="s">
         <v>228</v>
       </c>
-      <c r="J32" t="s">
+      <c r="N32" t="s">
         <v>229</v>
-      </c>
-      <c r="K32" t="s">
-        <v>230</v>
-      </c>
-      <c r="L32" t="s">
-        <v>99</v>
-      </c>
-      <c r="M32" t="s">
-        <v>231</v>
-      </c>
-      <c r="N32" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="H33" t="s">
+      <c r="B33" t="s">
+        <v>230</v>
+      </c>
+      <c r="I33" t="s">
+        <v>231</v>
+      </c>
+      <c r="J33" t="s">
+        <v>232</v>
+      </c>
+      <c r="K33" t="s">
+        <v>118</v>
+      </c>
+      <c r="L33" t="s">
         <v>233</v>
       </c>
-      <c r="I33" t="s">
+      <c r="M33" t="s">
         <v>234</v>
       </c>
-      <c r="J33" t="s">
+      <c r="N33" t="s">
         <v>235</v>
-      </c>
-      <c r="K33" t="s">
-        <v>236</v>
-      </c>
-      <c r="L33" t="s">
-        <v>99</v>
-      </c>
-      <c r="M33" t="s">
-        <v>237</v>
-      </c>
-      <c r="N33" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="H34" t="s">
-        <v>239</v>
+      <c r="B34" t="s">
+        <v>243</v>
       </c>
       <c r="I34" t="s">
-        <v>131</v>
+        <v>244</v>
       </c>
       <c r="J34" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K34" t="s">
-        <v>241</v>
+        <v>118</v>
       </c>
       <c r="L34" t="s">
-        <v>99</v>
+        <v>246</v>
       </c>
       <c r="M34" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="N34" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="H35" t="s">
-        <v>244</v>
+      <c r="B35" t="s">
+        <v>249</v>
       </c>
       <c r="I35" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="J35" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K35" t="s">
-        <v>247</v>
+        <v>118</v>
       </c>
       <c r="L35" t="s">
-        <v>99</v>
+        <v>252</v>
       </c>
       <c r="M35" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="N35" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="H36" t="s">
-        <v>250</v>
+      <c r="B36" t="s">
+        <v>255</v>
       </c>
       <c r="I36" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="J36" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K36" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="L36" t="s">
-        <v>99</v>
+        <v>258</v>
       </c>
       <c r="M36" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="N36" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="H37" t="s">
-        <v>256</v>
+      <c r="B37" t="s">
+        <v>261</v>
       </c>
       <c r="I37" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="J37" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K37" t="s">
-        <v>259</v>
+        <v>118</v>
       </c>
       <c r="L37" t="s">
-        <v>99</v>
+        <v>264</v>
       </c>
       <c r="M37" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="N37" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="H38" t="s">
-        <v>262</v>
+      <c r="B38" t="s">
+        <v>267</v>
       </c>
       <c r="I38" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="J38" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K38" t="s">
-        <v>265</v>
+        <v>118</v>
       </c>
       <c r="L38" t="s">
-        <v>99</v>
+        <v>270</v>
       </c>
       <c r="M38" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="N38" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="H39" t="s">
-        <v>268</v>
+      <c r="B39" t="s">
+        <v>273</v>
       </c>
       <c r="I39" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="J39" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K39" t="s">
-        <v>271</v>
+        <v>118</v>
       </c>
       <c r="L39" t="s">
-        <v>99</v>
+        <v>276</v>
       </c>
       <c r="M39" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="N39" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="H40" t="s">
-        <v>274</v>
+      <c r="B40" t="s">
+        <v>279</v>
       </c>
       <c r="I40" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J40" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K40" t="s">
-        <v>277</v>
+        <v>118</v>
       </c>
       <c r="L40" t="s">
-        <v>99</v>
+        <v>282</v>
       </c>
       <c r="M40" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="N40" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="H41" t="s">
-        <v>280</v>
+      <c r="B41" t="s">
+        <v>285</v>
       </c>
       <c r="I41" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="J41" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K41" t="s">
-        <v>283</v>
+        <v>118</v>
       </c>
       <c r="L41" t="s">
-        <v>99</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="H42" t="s">
-        <v>286</v>
+      <c r="B42" t="s">
+        <v>291</v>
       </c>
       <c r="I42" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J42" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K42" t="s">
-        <v>289</v>
+        <v>118</v>
       </c>
       <c r="L42" t="s">
-        <v>99</v>
+        <v>294</v>
       </c>
       <c r="M42" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N42" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="H43" t="s">
-        <v>292</v>
+      <c r="B43" t="s">
+        <v>297</v>
       </c>
       <c r="I43" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J43" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K43" t="s">
-        <v>295</v>
+        <v>118</v>
       </c>
       <c r="L43" t="s">
-        <v>99</v>
+        <v>300</v>
       </c>
       <c r="M43" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="N43" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="H44" t="s">
-        <v>298</v>
+      <c r="B44" t="s">
+        <v>303</v>
       </c>
       <c r="I44" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J44" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K44" t="s">
-        <v>301</v>
+        <v>118</v>
       </c>
       <c r="L44" t="s">
-        <v>99</v>
+        <v>306</v>
       </c>
       <c r="M44" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="N44" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="H45" t="s">
-        <v>304</v>
+      <c r="B45" t="s">
+        <v>309</v>
       </c>
       <c r="I45" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J45" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K45" t="s">
-        <v>307</v>
+        <v>118</v>
       </c>
       <c r="L45" t="s">
-        <v>99</v>
+        <v>312</v>
       </c>
       <c r="M45" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="N45" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="H46" t="s">
-        <v>310</v>
+      <c r="B46" t="s">
+        <v>315</v>
       </c>
       <c r="I46" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J46" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K46" t="s">
-        <v>313</v>
+        <v>118</v>
       </c>
       <c r="L46" t="s">
-        <v>99</v>
+        <v>318</v>
       </c>
       <c r="M46" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="N46" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A47" s="1">
-        <v>45</v>
-      </c>
-      <c r="H47" t="s">
-        <v>316</v>
-      </c>
-      <c r="I47" t="s">
-        <v>317</v>
-      </c>
-      <c r="J47" t="s">
-        <v>318</v>
-      </c>
-      <c r="K47" t="s">
-        <v>319</v>
-      </c>
-      <c r="L47" t="s">
-        <v>99</v>
-      </c>
-      <c r="M47" t="s">
         <v>320</v>
-      </c>
-      <c r="N47" t="s">
-        <v>321</v>
       </c>
     </row>
   </sheetData>
